--- a/backend/数据模板/模板-成绩汇总.xlsx
+++ b/backend/数据模板/模板-成绩汇总.xlsx
@@ -30,9 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>课程号</t>
   </si>
   <si>
     <t>课程名称</t>
@@ -1094,23 +1097,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.22727272727273" style="1" customWidth="1"/>
-    <col min="2" max="3" width="11.4363636363636" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.45454545454546" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="12.6272727272727" style="1"/>
-    <col min="9" max="9" width="7.78181818181818" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0181818181818" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.97272727272727" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="2" max="4" width="11.4363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.45454545454546" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.9" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="12.6272727272727" style="1"/>
+    <col min="10" max="10" width="7.78181818181818" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.0181818181818" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.97272727272727" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" spans="1:15">
+    <row r="1" customFormat="1" ht="19" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1126,16 +1129,16 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -1150,14 +1153,17 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" ht="16.35" customHeight="1" spans="1:15">
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="16.35" customHeight="1" spans="1:16">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1170,8 +1176,9 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
-    </row>
-    <row r="3" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" ht="16.35" customHeight="1" spans="1:16">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1184,8 +1191,9 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-    </row>
-    <row r="4" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" ht="16.35" customHeight="1" spans="1:16">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1198,8 +1206,9 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-    </row>
-    <row r="5" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" ht="16.35" customHeight="1" spans="1:16">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1212,8 +1221,9 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-    </row>
-    <row r="6" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" ht="16.35" customHeight="1" spans="1:16">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1226,8 +1236,9 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-    </row>
-    <row r="7" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" ht="16.35" customHeight="1" spans="1:16">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1240,8 +1251,9 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-    </row>
-    <row r="8" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" ht="16.35" customHeight="1" spans="1:16">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1254,8 +1266,9 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-    </row>
-    <row r="9" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" ht="16.35" customHeight="1" spans="1:16">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1268,8 +1281,9 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-    </row>
-    <row r="10" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" ht="16.35" customHeight="1" spans="1:16">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1282,8 +1296,9 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-    </row>
-    <row r="11" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" ht="16.35" customHeight="1" spans="1:16">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1296,8 +1311,9 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-    </row>
-    <row r="12" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" ht="16.35" customHeight="1" spans="1:16">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1310,8 +1326,9 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-    </row>
-    <row r="13" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" ht="16.35" customHeight="1" spans="1:16">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1324,8 +1341,9 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-    </row>
-    <row r="14" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" ht="16.35" customHeight="1" spans="1:16">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1338,8 +1356,9 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-    </row>
-    <row r="15" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" ht="16.35" customHeight="1" spans="1:16">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1352,8 +1371,9 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-    </row>
-    <row r="16" ht="16.35" customHeight="1" spans="1:15">
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" ht="16.35" customHeight="1" spans="1:16">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1366,8 +1386,9 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-    </row>
-    <row r="17" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" ht="16.35" customHeight="1" spans="1:14">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1380,8 +1401,9 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-    </row>
-    <row r="18" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" ht="16.35" customHeight="1" spans="1:14">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1394,8 +1416,9 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-    </row>
-    <row r="19" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" ht="16.35" customHeight="1" spans="1:14">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1408,8 +1431,9 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-    </row>
-    <row r="20" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" ht="16.35" customHeight="1" spans="1:14">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1422,8 +1446,9 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-    </row>
-    <row r="21" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" ht="16.35" customHeight="1" spans="1:14">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1436,8 +1461,9 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-    </row>
-    <row r="22" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" ht="16.35" customHeight="1" spans="1:14">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1450,8 +1476,9 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-    </row>
-    <row r="23" ht="16.35" customHeight="1" spans="1:13">
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" ht="16.35" customHeight="1" spans="1:14">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1464,9 +1491,9 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="D24" s="8"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -1476,6 +1503,7 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
